--- a/outputs/history-import-20261013/wealthdesk-history-template.xlsx
+++ b/outputs/history-import-20261013/wealthdesk-history-template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="1" r:id="R609626bd16224011"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度總覽" sheetId="2" r:id="R409f07610ed94e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行餘額" sheetId="3" r:id="Re7a92200adbd4af4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史持倉" sheetId="4" r:id="R6701307a0e684c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="1" r:id="Rfe99befd7784462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度總覽" sheetId="2" r:id="R5f40677e306e4be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行餘額" sheetId="3" r:id="R98ca964ba3c3419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史持倉" sheetId="4" r:id="R5c8f43a086274cb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -559,13 +559,13 @@
         <x:v>銀行餘額</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>月份、銀行、帳戶代稱、幣別、月末餘額</x:v>
+        <x:v>月份、銀行、帳戶用途、幣別、月末餘額</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>每個帳戶每月一列；代稱可使用主要活存、薪轉帳戶等</x:v>
+        <x:v>每個帳戶每月一列；用途可使用主要活存、薪轉帳戶等</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
@@ -663,7 +663,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="D27" s="18" t="str">
-        <x:v>相同月份內，代號/券商/帳戶或銀行/帳戶代稱不可重複</x:v>
+        <x:v>同月份內，代號/券商/帳戶或銀行/帳戶用途不可重複</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9729,7 +9729,7 @@
         <x:v>銀行</x:v>
       </x:c>
       <x:c r="C1" s="22" t="str">
-        <x:v>帳戶代稱</x:v>
+        <x:v>帳戶用途</x:v>
       </x:c>
       <x:c r="D1" s="22" t="str">
         <x:v>幣別</x:v>
